--- a/IONQ.xlsx
+++ b/IONQ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Martin Shkreli - DL\models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E1171B1-2B4E-415E-A89F-C430E52D5960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EA1A146-E8B6-47D6-927A-EC78318E9D51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="50380" yWindow="4260" windowWidth="17370" windowHeight="13000" activeTab="1" xr2:uid="{AB3C49AB-D501-4FD3-A043-98BB663A0B7E}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22150" windowHeight="20350" activeTab="1" xr2:uid="{AB3C49AB-D501-4FD3-A043-98BB663A0B7E}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -999,14 +999,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>18257</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>23141</xdr:colOff>
       <xdr:row>0</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>18257</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>23141</xdr:colOff>
       <xdr:row>74</xdr:row>
       <xdr:rowOff>43542</xdr:rowOff>
     </xdr:to>
@@ -1023,8 +1023,8 @@
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="13154820" y="0"/>
-          <a:ext cx="0" cy="11195730"/>
+          <a:off x="13729372" y="0"/>
+          <a:ext cx="0" cy="11996196"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
